--- a/artfynd/A 36596-2024 artfynd.xlsx
+++ b/artfynd/A 36596-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122454169</v>
       </c>
       <c r="B2" t="n">
-        <v>89424</v>
+        <v>89436</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 36596-2024 artfynd.xlsx
+++ b/artfynd/A 36596-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122454169</v>
       </c>
       <c r="B2" t="n">
-        <v>89436</v>
+        <v>89440</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 36596-2024 artfynd.xlsx
+++ b/artfynd/A 36596-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122454169</v>
       </c>
       <c r="B2" t="n">
-        <v>89440</v>
+        <v>89445</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>1593</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Lakritsmusseron</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 36596-2024 artfynd.xlsx
+++ b/artfynd/A 36596-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122454169</v>
       </c>
       <c r="B2" t="n">
-        <v>89445</v>
+        <v>89458</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>1593</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Lakritsmusseron</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 36596-2024 artfynd.xlsx
+++ b/artfynd/A 36596-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122454169</v>
       </c>
       <c r="B2" t="n">
-        <v>89458</v>
+        <v>89470</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 36596-2024 artfynd.xlsx
+++ b/artfynd/A 36596-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122454169</v>
       </c>
       <c r="B2" t="n">
-        <v>89470</v>
+        <v>89471</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 36596-2024 artfynd.xlsx
+++ b/artfynd/A 36596-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122454169</v>
       </c>
       <c r="B2" t="n">
-        <v>89471</v>
+        <v>89474</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 36596-2024 artfynd.xlsx
+++ b/artfynd/A 36596-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122454169</v>
       </c>
       <c r="B2" t="n">
-        <v>89577</v>
+        <v>89581</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 36596-2024 artfynd.xlsx
+++ b/artfynd/A 36596-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>122454169</v>
       </c>
       <c r="B2" t="n">
-        <v>89581</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -774,6 +769,200 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122454170</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90659</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1593</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Lakritsmusseron</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tricholoma apium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Jul.Schäff.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norstjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>529789</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6628853</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122454171</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90674</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1596</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jättemusseron</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tricholoma colossus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norstjärn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>529788</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6628815</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
